--- a/arquivo_final.xlsx
+++ b/arquivo_final.xlsx
@@ -1031,9 +1031,110 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>DGREB5454</t>
+        </is>
+      </c>
+      <c r="B1" t="n">
+        <v>2397</v>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>00700</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>PN0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DGREB5457</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>5147</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>00800</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PN0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>DGREB5460</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>8679</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>00700</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PN0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>DGREB5466</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>8844</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>00700</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PN0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DGREB5469</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1085</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>00700</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PN0001</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1044,9 +1145,130 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>DGREB5455</t>
+        </is>
+      </c>
+      <c r="B1" t="n">
+        <v>3777</v>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>00900</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>VRA001</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DGREB5458</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>8448</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>00700</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>VRA001</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>DGREB5461</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>7763</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>00900</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VRA001</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>DGREB5464</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>9188</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>00700</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VRA001</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DGREB5467</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>5642</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>00900</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VRA001</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DGREB5470</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4962</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>00700</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VRA001</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1057,9 +1279,90 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>DGREB5459</t>
+        </is>
+      </c>
+      <c r="B1" t="n">
+        <v>5463</v>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>00800</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>HV0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DGREB5465</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>4185</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>00900</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>HV0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>DGREB5468</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>5944</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>00900</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>HV0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>DGREB5471</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>5555</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>00900</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>HV0001</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>